--- a/artfynd/A 60904-2025 artfynd.xlsx
+++ b/artfynd/A 60904-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133617768</v>
+        <v>133616632</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460228</v>
+        <v>460210</v>
       </c>
       <c r="R3" t="n">
-        <v>6905203</v>
+        <v>6905059</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på marken efter avverkning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133616632</v>
+        <v>133617768</v>
       </c>
       <c r="B4" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460210</v>
+        <v>460228</v>
       </c>
       <c r="R4" t="n">
-        <v>6905059</v>
+        <v>6905203</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på marken efter avverkning.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 60904-2025 artfynd.xlsx
+++ b/artfynd/A 60904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133617096</v>
       </c>
       <c r="B2" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133616632</v>
+        <v>133617768</v>
       </c>
       <c r="B3" t="n">
-        <v>79923</v>
+        <v>79334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460210</v>
+        <v>460228</v>
       </c>
       <c r="R3" t="n">
-        <v>6905059</v>
+        <v>6905203</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på marken efter avverkning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133617768</v>
+        <v>133616632</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>79924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460228</v>
+        <v>460210</v>
       </c>
       <c r="R4" t="n">
-        <v>6905203</v>
+        <v>6905059</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på marken efter avverkning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>133616618</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>133617977</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>133617937</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>133617596</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 60904-2025 artfynd.xlsx
+++ b/artfynd/A 60904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133617096</v>
       </c>
       <c r="B2" t="n">
-        <v>98003</v>
+        <v>98011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>133617937</v>
       </c>
       <c r="B7" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60904-2025 artfynd.xlsx
+++ b/artfynd/A 60904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133617096</v>
       </c>
       <c r="B2" t="n">
-        <v>98011</v>
+        <v>98039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133617768</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>133616632</v>
       </c>
       <c r="B4" t="n">
-        <v>79924</v>
+        <v>79938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>133616618</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>133617977</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>133617937</v>
       </c>
       <c r="B7" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>133617596</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>133616491</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 60904-2025 artfynd.xlsx
+++ b/artfynd/A 60904-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133617096</v>
       </c>
       <c r="B2" t="n">
-        <v>98039</v>
+        <v>98049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>133617768</v>
       </c>
       <c r="B3" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>133616632</v>
       </c>
       <c r="B4" t="n">
-        <v>79938</v>
+        <v>79948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>133616618</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>133617977</v>
       </c>
       <c r="B6" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>133617937</v>
       </c>
       <c r="B7" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>133617596</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>133616491</v>
       </c>
       <c r="B9" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
